--- a/data/trans_dic/P16A06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,84</t>
+          <t>1,07; 3,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,43</t>
+          <t>0,92; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,08</t>
+          <t>1,37; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,33</t>
+          <t>3,46; 7,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,31</t>
+          <t>1,44; 5,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,85</t>
+          <t>1,93; 6,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,75</t>
+          <t>1,59; 5,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,14</t>
+          <t>4,3; 7,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,69</t>
+          <t>1,48; 3,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 4,6</t>
+          <t>1,58; 4,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,27</t>
+          <t>1,78; 4,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,89</t>
+          <t>4,25; 6,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,31</t>
+          <t>0,97; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,66</t>
+          <t>1,0; 4,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,14</t>
+          <t>1,03; 4,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,34</t>
+          <t>2,77; 6,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,91</t>
+          <t>0,78; 4,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,25</t>
+          <t>0,88; 3,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,89</t>
+          <t>1,73; 5,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,66</t>
+          <t>6,08; 10,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,3</t>
+          <t>1,08; 3,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,91</t>
+          <t>1,2; 3,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,13</t>
+          <t>1,7; 4,11</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,58</t>
+          <t>4,79; 7,62</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,76</t>
+          <t>0,66; 2,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,98</t>
+          <t>1,83; 4,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,05</t>
+          <t>1,25; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,5</t>
+          <t>1,16; 6,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,78</t>
+          <t>1,73; 7,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,08</t>
+          <t>2,47; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 14,61</t>
+          <t>4,64; 14,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 16,62</t>
+          <t>8,74; 16,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,21</t>
+          <t>1,21; 3,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,22</t>
+          <t>2,53; 5,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,74</t>
+          <t>2,57; 5,65</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 8,37</t>
+          <t>2,37; 8,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,4</t>
+          <t>1,67; 3,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,6</t>
+          <t>1,02; 2,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,49</t>
+          <t>2,34; 4,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,26</t>
+          <t>4,93; 7,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,77</t>
+          <t>2,2; 5,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,98</t>
+          <t>2,92; 5,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,27</t>
+          <t>4,05; 7,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,92</t>
+          <t>2,79; 7,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,63</t>
+          <t>2,07; 3,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,59</t>
+          <t>1,96; 3,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,15</t>
+          <t>3,34; 5,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,99</t>
+          <t>4,26; 7,09</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,4</t>
+          <t>1,52; 5,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,95</t>
+          <t>1,14; 3,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,52</t>
+          <t>1,94; 4,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,84</t>
+          <t>3,81; 7,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,52</t>
+          <t>2,41; 5,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 10,78</t>
+          <t>6,72; 10,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 12,25</t>
+          <t>7,96; 12,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,08</t>
+          <t>10,75; 17,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,76</t>
+          <t>2,33; 4,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,73</t>
+          <t>4,82; 7,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,24</t>
+          <t>5,48; 8,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,12</t>
+          <t>8,97; 13,08</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 2,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,24</t>
+          <t>1,24; 9,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,28</t>
+          <t>4,46; 7,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,58</t>
+          <t>6,96; 10,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,38</t>
+          <t>8,37; 12,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,07; 14,77</t>
+          <t>11,1; 15,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,68</t>
+          <t>3,62; 5,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,37</t>
+          <t>5,65; 8,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,08</t>
+          <t>6,77; 9,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,95; 12,35</t>
+          <t>9,05; 12,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,46</t>
+          <t>1,48; 2,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,6</t>
+          <t>1,5; 2,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 3,29</t>
+          <t>2,12; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 5,78</t>
+          <t>3,87; 5,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,52; 4,91</t>
+          <t>3,57; 4,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 7,16</t>
+          <t>5,49; 7,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,47</t>
+          <t>6,69; 8,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 11,0</t>
+          <t>8,09; 10,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,51</t>
+          <t>2,68; 3,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 4,71</t>
+          <t>3,65; 4,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,74</t>
+          <t>4,62; 5,73</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,24</t>
+          <t>6,47; 8,17</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5137; 18187</t>
+          <t>5080; 17770</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3987; 19368</t>
+          <t>4017; 19093</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5734; 21804</t>
+          <t>5884; 21139</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17702; 37038</t>
+          <t>17499; 37071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4583; 16277</t>
+          <t>4417; 16747</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5792; 21532</t>
+          <t>6083; 21450</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5714; 19943</t>
+          <t>5526; 18670</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18877; 36429</t>
+          <t>19254; 35127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11778; 28813</t>
+          <t>11553; 28701</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11983; 34598</t>
+          <t>11864; 32490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13643; 33139</t>
+          <t>13786; 33353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40367; 65644</t>
+          <t>40468; 66090</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2910; 15812</t>
+          <t>3545; 15462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4048; 19395</t>
+          <t>4143; 19711</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3929; 15634</t>
+          <t>3890; 15214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12295; 28669</t>
+          <t>12543; 28838</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2972; 14558</t>
+          <t>2917; 15063</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2999; 14261</t>
+          <t>2944; 13186</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6841; 21917</t>
+          <t>6429; 20802</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23180; 40771</t>
+          <t>23254; 39914</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7722; 24414</t>
+          <t>7952; 24557</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9184; 29339</t>
+          <t>9027; 28503</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12994; 30975</t>
+          <t>12775; 30804</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38968; 63273</t>
+          <t>39970; 63608</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3518; 14958</t>
+          <t>3594; 14370</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11960; 31176</t>
+          <t>11435; 30747</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6843; 21145</t>
+          <t>6524; 20264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8294; 43448</t>
+          <t>7783; 44070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2870; 13056</t>
+          <t>2900; 12397</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6346; 20838</t>
+          <t>6380; 21314</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8676; 24265</t>
+          <t>7715; 24101</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15242; 27744</t>
+          <t>14587; 27533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8330; 22824</t>
+          <t>8577; 23056</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22700; 46152</t>
+          <t>22342; 45974</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18064; 39490</t>
+          <t>17674; 38846</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18041; 69873</t>
+          <t>19774; 69337</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20444; 42061</t>
+          <t>20735; 41954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10795; 30102</t>
+          <t>11759; 30621</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25341; 51663</t>
+          <t>26877; 50533</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49470; 75161</t>
+          <t>51015; 78232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15027; 34036</t>
+          <t>15718; 35708</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21781; 45767</t>
+          <t>22387; 45729</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33194; 60009</t>
+          <t>33475; 59944</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31667; 77430</t>
+          <t>27231; 75900</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41902; 70850</t>
+          <t>40397; 69616</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37342; 68982</t>
+          <t>37740; 68227</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65149; 101804</t>
+          <t>65917; 100818</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82656; 140656</t>
+          <t>85761; 142711</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5233; 18875</t>
+          <t>5318; 18675</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5970; 20110</t>
+          <t>5831; 18838</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11573; 28068</t>
+          <t>12034; 30179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18833; 37139</t>
+          <t>18035; 36832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13128; 31414</t>
+          <t>13705; 33295</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49785; 81755</t>
+          <t>50940; 81024</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57752; 90406</t>
+          <t>58733; 92798</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>87143; 143238</t>
+          <t>90195; 147207</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21674; 43748</t>
+          <t>21418; 43612</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61011; 97967</t>
+          <t>61139; 94358</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74251; 111969</t>
+          <t>74448; 112347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>120242; 172172</t>
+          <t>117760; 171636</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1925</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7526</t>
+          <t>0; 7408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2968; 27025</t>
+          <t>2981; 23147</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58203; 90962</t>
+          <t>55747; 88554</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76438; 116906</t>
+          <t>76931; 116265</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>91411; 133988</t>
+          <t>90556; 131987</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84118; 112297</t>
+          <t>84369; 114195</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56309; 87827</t>
+          <t>56074; 89644</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75478; 114828</t>
+          <t>77525; 114014</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91495; 138038</t>
+          <t>92640; 135023</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>89601; 123561</t>
+          <t>90528; 125829</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>50605; 80430</t>
+          <t>48391; 82440</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53078; 88872</t>
+          <t>51307; 86945</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>72807; 111241</t>
+          <t>71776; 109919</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>131756; 195115</t>
+          <t>130752; 197672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119030; 165976</t>
+          <t>120437; 167558</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>191227; 253119</t>
+          <t>194184; 252307</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>235729; 299234</t>
+          <t>236102; 302068</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>286637; 393183</t>
+          <t>289134; 392082</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>176279; 233182</t>
+          <t>177889; 236476</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>259227; 327175</t>
+          <t>253367; 323436</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>319359; 397201</t>
+          <t>319251; 396441</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>448933; 572615</t>
+          <t>449554; 567470</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,75</t>
+          <t>0,94; 3,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,37</t>
+          <t>0,92; 4,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,93</t>
+          <t>1,34; 4,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 7,34</t>
+          <t>3,34; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,46</t>
+          <t>1,39; 5,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,82</t>
+          <t>1,9; 7,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,38</t>
+          <t>1,48; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,85</t>
+          <t>4,2; 7,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,68</t>
+          <t>1,52; 3,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,32</t>
+          <t>1,74; 4,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,3</t>
+          <t>1,77; 4,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,94</t>
+          <t>4,13; 6,94</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,21</t>
+          <t>0,78; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,74</t>
+          <t>0,98; 4,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,03</t>
+          <t>0,88; 3,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,38</t>
+          <t>2,69; 6,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,05</t>
+          <t>0,77; 3,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,93</t>
+          <t>0,88; 3,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,59</t>
+          <t>1,84; 5,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,08; 10,43</t>
+          <t>6,03; 10,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,32</t>
+          <t>1,06; 3,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,79</t>
+          <t>1,23; 3,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,11</t>
+          <t>1,7; 4,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,62</t>
+          <t>4,73; 7,61</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,65</t>
+          <t>0,63; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,91</t>
+          <t>1,85; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,88</t>
+          <t>1,28; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 6,59</t>
+          <t>3,99; 8,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,39</t>
+          <t>1,68; 7,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 8,26</t>
+          <t>2,81; 7,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,51</t>
+          <t>4,71; 13,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 16,5</t>
+          <t>8,71; 16,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,25</t>
+          <t>1,21; 3,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,2</t>
+          <t>2,47; 5,12</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,65</t>
+          <t>2,72; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,3</t>
+          <t>5,95; 9,87</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,39</t>
+          <t>1,61; 3,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,64</t>
+          <t>0,96; 2,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,4</t>
+          <t>2,18; 4,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,56</t>
+          <t>4,74; 7,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,0</t>
+          <t>2,3; 5,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,97</t>
+          <t>2,81; 5,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,26</t>
+          <t>4,07; 7,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,77</t>
+          <t>5,96; 8,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,57</t>
+          <t>2,13; 3,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,55</t>
+          <t>1,98; 3,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,1</t>
+          <t>3,28; 5,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,09</t>
+          <t>5,64; 7,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,34</t>
+          <t>1,63; 5,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,7</t>
+          <t>1,14; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,86</t>
+          <t>1,86; 4,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,78</t>
+          <t>3,7; 7,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,85</t>
+          <t>2,28; 5,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 10,68</t>
+          <t>6,58; 10,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 12,57</t>
+          <t>7,9; 12,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 17,55</t>
+          <t>13,5; 17,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,75</t>
+          <t>2,39; 4,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,44</t>
+          <t>4,81; 7,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,27</t>
+          <t>5,6; 8,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,08</t>
+          <t>9,88; 12,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,58</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,62</t>
+          <t>1,62; 9,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,09</t>
+          <t>4,58; 7,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,96; 10,52</t>
+          <t>6,84; 10,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,2</t>
+          <t>8,36; 12,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,02</t>
+          <t>10,84; 14,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 5,79</t>
+          <t>3,68; 5,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,32</t>
+          <t>5,55; 8,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,86</t>
+          <t>6,76; 10,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,05; 12,57</t>
+          <t>8,98; 12,67</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,52</t>
+          <t>1,57; 2,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,55</t>
+          <t>1,54; 2,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,25</t>
+          <t>2,14; 3,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,86</t>
+          <t>4,6; 6,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,57; 4,96</t>
+          <t>3,51; 4,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,13</t>
+          <t>5,55; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 8,55</t>
+          <t>6,67; 8,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,09; 10,97</t>
+          <t>9,67; 11,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,56</t>
+          <t>2,67; 3,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,65</t>
+          <t>3,68; 4,68</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,73</t>
+          <t>4,62; 5,74</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,17</t>
+          <t>7,36; 8,52</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51775</t>
+          <t>55031</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5080; 17770</t>
+          <t>4439; 17262</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4017; 19093</t>
+          <t>4004; 19763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5884; 21139</t>
+          <t>5731; 20366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17499; 37071</t>
+          <t>18414; 38122</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4417; 16747</t>
+          <t>4273; 16656</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6083; 21450</t>
+          <t>5983; 22252</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5526; 18670</t>
+          <t>5128; 18921</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19254; 35127</t>
+          <t>20525; 37955</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11553; 28701</t>
+          <t>11856; 28705</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11864; 32490</t>
+          <t>13116; 33340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13786; 33353</t>
+          <t>13732; 33697</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40468; 66090</t>
+          <t>42932; 72073</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>33770</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49881</t>
+          <t>53709</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3545; 15462</t>
+          <t>2867; 15174</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4143; 19711</t>
+          <t>4076; 18959</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3890; 15214</t>
+          <t>3319; 15019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12543; 28838</t>
+          <t>13020; 29813</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2917; 15063</t>
+          <t>2857; 13842</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2944; 13186</t>
+          <t>2944; 13332</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6429; 20802</t>
+          <t>6847; 20963</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23254; 39914</t>
+          <t>25525; 42754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7952; 24557</t>
+          <t>7867; 23388</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9027; 28503</t>
+          <t>9256; 26930</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12775; 30804</t>
+          <t>12725; 31614</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39970; 63608</t>
+          <t>42874; 68945</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>22341</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45540</t>
+          <t>49789</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3594; 14370</t>
+          <t>3421; 13941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11435; 30747</t>
+          <t>11606; 31206</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6524; 20264</t>
+          <t>6673; 21469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7783; 44070</t>
+          <t>18796; 38967</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2900; 12397</t>
+          <t>2824; 13185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6380; 21314</t>
+          <t>7245; 20507</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7715; 24101</t>
+          <t>7816; 23086</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14587; 27533</t>
+          <t>16340; 30301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8577; 23056</t>
+          <t>8617; 22962</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22342; 45974</t>
+          <t>21817; 45286</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17674; 38846</t>
+          <t>18724; 39690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19774; 69337</t>
+          <t>39235; 65084</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>67241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>118771</t>
+          <t>129209</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20735; 41954</t>
+          <t>19888; 41879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11759; 30621</t>
+          <t>11167; 30348</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26877; 50533</t>
+          <t>25089; 49806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51015; 78232</t>
+          <t>53617; 82891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15718; 35708</t>
+          <t>16420; 37386</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22387; 45729</t>
+          <t>21540; 45380</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33475; 59944</t>
+          <t>33592; 57937</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27231; 75900</t>
+          <t>51223; 74616</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40397; 69616</t>
+          <t>41654; 69660</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37740; 68227</t>
+          <t>38057; 68441</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65917; 100818</t>
+          <t>64749; 100430</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85761; 142711</t>
+          <t>112352; 149052</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>120962</t>
+          <t>126020</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>147647</t>
+          <t>155772</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5318; 18675</t>
+          <t>5691; 19016</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5831; 18838</t>
+          <t>5784; 18757</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12034; 30179</t>
+          <t>11542; 28907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18035; 36832</t>
+          <t>20959; 41653</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>13705; 33295</t>
+          <t>12943; 32006</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50940; 81024</t>
+          <t>49885; 81533</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58733; 92798</t>
+          <t>58292; 92535</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90195; 147207</t>
+          <t>112001; 144304</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21418; 43612</t>
+          <t>21949; 44024</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>61139; 94358</t>
+          <t>60970; 94119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74448; 112347</t>
+          <t>76049; 112663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>117760; 171636</t>
+          <t>137926; 177649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>9088</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>97860</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>105954</t>
+          <t>115774</t>
         </is>
       </c>
     </row>
@@ -2977,52 +2977,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7408</t>
+          <t>0; 8397</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2981; 23147</t>
+          <t>3841; 22755</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55747; 88554</t>
+          <t>57136; 88514</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76931; 116265</t>
+          <t>75569; 116059</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>90556; 131987</t>
+          <t>90407; 133120</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84369; 114195</t>
+          <t>91403; 122420</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56074; 89644</t>
+          <t>56942; 89734</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>77525; 114014</t>
+          <t>76111; 117095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92640; 135023</t>
+          <t>92498; 136990</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>90528; 125829</t>
+          <t>96964; 136873</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>166941</t>
+          <t>180331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>352627</t>
+          <t>378953</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>519568</t>
+          <t>559284</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>48391; 82440</t>
+          <t>51422; 83127</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>51307; 86945</t>
+          <t>52567; 89308</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71776; 109919</t>
+          <t>72365; 109070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>130752; 197672</t>
+          <t>158195; 207416</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>120437; 167558</t>
+          <t>118587; 167186</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>194184; 252307</t>
+          <t>196429; 251688</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>236102; 302068</t>
+          <t>235602; 302219</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>289134; 392082</t>
+          <t>351082; 411570</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>177889; 236476</t>
+          <t>177686; 235105</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>253367; 323436</t>
+          <t>255701; 325111</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>319251; 396441</t>
+          <t>319236; 397169</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>449554; 567470</t>
+          <t>520697; 602747</t>
         </is>
       </c>
     </row>
